--- a/performance_tracking_forms/006_student_behavior_tracking_form--performance_tracking_forms.xlsx
+++ b/performance_tracking_forms/006_student_behavior_tracking_form--performance_tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>General Behavior</t>
+          <t>General Behavior Phone</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Student Behavior Note</t>
+          <t>Student Behavior Note Date</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>teacher_attendance</t>
+          <t>teacher_attendance_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>General Behavior Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Teacher Attendance Email</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>general_behavior_phone</t>
+          <t>general_behavior_phone_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>General Behavior Phone 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>during_hours_phone</t>
+          <t>during_hours_phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone During Hours</t>
+          <t>During Hours Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>time_out</t>
+          <t>time_out_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Time Out</t>
+          <t>Time Out 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>teacher_attendance</t>
+          <t>teacher_attendance_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Teacher Attendance</t>
+          <t>Teacher Attendance 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'excellent',_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'excellent', 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'poor',_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'poor', 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
